--- a/generated/sources/reports/americas/AMER_Retail_Monthly_FY26_P08_Sep.xlsx
+++ b/generated/sources/reports/americas/AMER_Retail_Monthly_FY26_P08_Sep.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="66">
   <si>
-    <t>MONCLER USA INC.  -  RETAIL MONTHLY SALES REPORT</t>
+    <t>VALENTINO USA INC.  -  RETAIL MONTHLY SALES REPORT</t>
   </si>
   <si>
     <t>FY2026  P08 (SEPTEMBER)  |  08/30/2026 - 10/03/2026  (5 wks, 4-5-4)  |  LY: 08/31/2025 - 10/04/2025  |  USD, CAD @ plan rate 1.37</t>
@@ -166,7 +166,7 @@
     <t>Comment</t>
   </si>
   <si>
-    <t>Campaign windows; ILVARO black/off-white requests (celebrity effect)</t>
+    <t>Campaign windows; IRIDIA black/off-white requests (celebrity effect)</t>
   </si>
   <si>
     <t>POS down 10/6 2:10-5:40pm; manual tickets keyed 10/7 -&gt; 10/6 understated, 10/7 overstated</t>
@@ -178,7 +178,7 @@
     <t>Pre-season, low traffic until Thanksgiving</t>
   </si>
   <si>
-    <t>ARNEB strong but many size exchanges (runs large)</t>
+    <t>ARTEM strong but many size exchanges (runs large)</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -205,10 +205,10 @@
     <t>Miami: A/C failure 9/3-9/5 (store open, clients left quickly). Repaired by vendor on 9/5.</t>
   </si>
   <si>
-    <t>Toronto: TIFF 9/10-9/20 drove traffic in Yorkville; ARNEB parka the best FW26 style in Canada but exchanges for size (fits large).</t>
-  </si>
-  <si>
-    <t>Genius POLARIS (launched 9/24) slow in US: fit runs small and price point; clients compare with the regular collection.</t>
+    <t>Toronto: TIFF 9/10-9/20 drove traffic in Yorkville; ARTEM parka the best FW26 style in Canada but exchanges for size (fits large).</t>
+  </si>
+  <si>
+    <t>Couture ASTRA (launched 9/24) slow in US: fit runs small and price point; clients compare with the regular collection.</t>
   </si>
   <si>
     <t>P09 to date: NYC02 POS outage on 10/6 (see P09 MTD tab). Aspen opens full schedule from Thanksgiving.</t>
